--- a/data-penerimaan-2026.xlsx
+++ b/data-penerimaan-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RUDI\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RUDI\2026\DATA LAYANAN\backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8CE17E-F9FF-4F95-BCDE-F6219DF7BF2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3D9FB0-AF9E-414D-94E4-064C26007543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="target" sheetId="1" r:id="rId1"/>
@@ -1063,7 +1063,6 @@
         <v>37946171</v>
       </c>
       <c r="E10" s="1">
-        <f>235805873-19612581</f>
         <v>216193292</v>
       </c>
       <c r="F10" s="1">
@@ -1447,22 +1446,26 @@
         <v>244079000</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3"/>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C19" s="1">
         <f>C14+B14</f>
         <v>10629156</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="E19" s="1">
+        <f>235805873-19612581</f>
+        <v>216193292</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3"/>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="3"/>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">

--- a/data-penerimaan-2026.xlsx
+++ b/data-penerimaan-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RUDI\2026\DATA LAYANAN\backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFDCFBE2-3B70-477A-B00F-E9B8A652FF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC1959-60F1-436E-ACC7-5D8B4B294E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2076,7 +2076,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>0</v>
+        <v>26000000</v>
       </c>
       <c r="C14" s="1">
         <v>26000000</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B16" s="4">
         <f t="shared" ref="B16:E16" si="0">SUM(B2:B15)</f>
-        <v>464898600</v>
+        <v>490898600</v>
       </c>
       <c r="C16" s="4">
         <f t="shared" si="0"/>
